--- a/extenbooks/S617.xlsx
+++ b/extenbooks/S617.xlsx
@@ -825,11 +825,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -951,6 +951,155 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DPR (markdown)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t># S617 — Employee Compensation (EC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>**Chapter**: 6 (supporting). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: billions_usd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Total compensation of all employees (productive + unproductive) — the denominator for ST 1987 / ST 2002 NSW ratios. Loaded from Appendix H.1 column `EC`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pass-through from `data/source/book_tables/book_tableH1_1948_1989.csv` column `EC`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1948 = 142.09B; 1989 = 3079.00B. Validator PASS at both endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Why this is a series</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>While EC is intermediate to many downstream ratios, registering it as a first-class series (S617) means every ratio that uses it (ES1101-1103, ES1201-1202, future productivity series) has a single audited source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/extenbooks/S617.xlsx
+++ b/extenbooks/S617.xlsx
@@ -450,19 +450,19 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">S617 — </t>
+          <t>S617 — Employee Compensation (EC)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>, units=</t>
+          <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -862,7 +862,11 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Employee Compensation (EC)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -870,7 +874,11 @@
           <t>Chapter</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -886,7 +894,11 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -894,7 +906,11 @@
           <t>Content Type</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -904,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>None–None</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -954,148 +970,185 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S617-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S617 — Employee Compensation (EC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 (supporting). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: billions_usd.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># S617 — Employee Compensation (EC)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Total compensation of all employees (productive + unproductive) — the denominator for ST 1987 / ST 2002 NSW ratios. Loaded from Appendix H.1 column `EC`.</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Chapter**: 6 (supporting). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: billions_usd.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pass-through from `data/source/book_tables/book_tableH1_1948_1989.csv` column `EC`.</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Total compensation of all employees (productive + unproductive) — the denominator for ST 1987 / ST 2002 NSW ratios. Loaded from Appendix H.1 column `EC`.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>## Reference</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1948 = 142.09B; 1989 = 3079.00B. Validator PASS at both endpoints.</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pass-through from `data/source/book_tables/book_tableH1_1948_1989.csv` column `EC`.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>## Why this is a series</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Reference</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>While EC is intermediate to many downstream ratios, registering it as a first-class series (S617) means every ratio that uses it (ES1101-1103, ES1201-1202, future productivity series) has a single audited source.</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1948 = 142.09B; 1989 = 3079.00B. Validator PASS at both endpoints.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>## Why this is a series</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>While EC is intermediate to many downstream ratios, registering it as a first-class series (S617) means every ratio that uses it (ES1101-1103, ES1201-1202, future productivity series) has a single audited source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1112,13 +1165,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No research JSON for S617</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>entry_id_or_type</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>content_or_quote</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>source_ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Productive worker wage bill Wp (= variable capital V*) falls relative to total wages W. Unproductive wage bill Wu rises sharply relative to Wp. This tells us that it is movement in relative employment levels, not in relative wage rates, which is crucial.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Surplus value S* approximately 2x most inclusive measure of profit-type income P+, where P+ = NNP - employee compensation.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Employee compensation is our starting point because it represents the direct cost incurred by capitalists for hiring labor power; to the individual capitalist this is the same as variable capital. But for the system as a whole, we must adjust for the net transfer between wage and salary workers and the state.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Both surplus value S* and profit-type income P rise strongly over the postwar period, but the former is much larger and rises somewhat faster. On the other hand variable capital V* (the productive worker wage bill) is much smaller and rises much more slowly than total employee compensation EC.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Thus the true rate of surplus value is not only almost four times as large as its naive counterpart, the profit/wage ratio P+/EC, but also moves very differently: the rate of surplus value rises by almost 50%, while the profit/wage ratio actually falls by almost 27%.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Variable capital is estimated from BLS production worker wages (wp) scaled by the NIPA employee-compensation-to-wages ratio x = EC/WS, then multiplied by productive employment Lp.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>methodology_derived</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S617 is a Chapter 6 series added late to the registry with minimal metadata. The registry entry contains only a status field ('book_period_validated'). Based on its ID placement (after S609, the last fully-defined Chapter 6 series), S617 likely represents a supplementary tax, benefit, or net social wage variant not covered by S601-S609.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>series_registry.json (S617: {status: 'book_period_validated'})</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The Chapter 6 series family covers the social wage framework: S601-S603 (tax components: personal, social insurance, property), S604 (total tax on workers), S605 (government benefits to workers), S606 (government services to workers), S607 (Net Social Wage = B_w + G_w - T_w), S608 (NSW/V* ratio), S609 (NSW/NI share). S617 may represent an additional ratio, alternative deflation, or extended decomposition within this framework.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>series_registry.json Chapter 6 series overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>No construction steps, subseries, name, units, or source file are specified in the registry. The series was likely added as a placeholder or late addition. Full metadata needs to be populated from the book or from the construction scripts.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>series_registry.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>305-307 (paraphrased from Appendix G)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sparse registry entry for a Chapter 6 series (status: book_period_validated only). Likely a supplementary social wage measure. Full definition pending — needs metadata population from book or construction scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Registry entry contains only status — no name, description, units, or construction steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Series purpose must be determined from book Chapter 6 or legacy scripts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>May need registry update once the series is fully characterized</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S608</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S609</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1515,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1179,7 +1561,64 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{"1948": 142.09, "1989": 3079.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S617.xlsx
+++ b/extenbooks/S617.xlsx
@@ -531,7 +531,7 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>209.3</v>
+        <v>209.37</v>
       </c>
     </row>
     <row r="10">
@@ -1126,7 +1126,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>While EC is intermediate to many downstream ratios, registering it as a first-class series (S617) means every ratio that uses it (ES1101-1103, ES1201-1202, future productivity series) has a single audited source.</t>
+          <t>While EC is intermediate to many downstream ratios, registering it as a first-class series (S617) means every ratio that uses it (XS1101-1103, XS1201-1202, future productivity series) has a single audited source.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S617.xlsx
+++ b/extenbooks/S617.xlsx
@@ -1165,7 +1165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sparse registry entry for a Chapter 6 series (status: book_period_validated only). Likely a supplementary social wage measure. Full definition pending — needs metadata population from book or construction scripts.</t>
+          <t>Total employee compensation EC = productive + unproductive wage bills, book Appendix H.1 column EC, 1948-1989. Reproduces the book exactly (1948=142.09, 1989=3079.0). WP-A 2026-07-01: corrected stale placeholder description (was mislabeled "Chapter 6 Supplementary Series"); the EC identity was already established in backfill_log 2026-05-19. No extension currently built (extension:null, book-period only); EC is trivially extendable via BEA NIPA Compensation of employees and is the denominator for downstream XS NSW ratios.</t>
         </is>
       </c>
     </row>
@@ -1452,19 +1452,19 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WP-A 2026-07-01: series_name/methodology_summary were stale placeholders speculating a supplementary social-wage variant; corrected to the confirmed Employee Compensation (EC) identity (backfill_log 2026-05-19). Registry chapter=6 but EC book home is Appendix H (used in Ch5 5.9 / Ch7 7.3) - chapter_ref already documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>S607</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S608</t>
+          <t>S607</t>
         </is>
       </c>
     </row>
@@ -1480,25 +1480,33 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
+          <t>S608</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>S609</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
